--- a/data/trans_dic/P19C02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,16; 38,61</t>
+          <t>26,15; 39,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,06; 31,03</t>
+          <t>19,68; 30,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,35</t>
+          <t>17,9; 29,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,85; 55,09</t>
+          <t>40,43; 54,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 42,35</t>
+          <t>28,32; 42,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,69; 32,31</t>
+          <t>20,33; 31,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 31,62</t>
+          <t>20,61; 32,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,52; 50,78</t>
+          <t>40,84; 50,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,81; 38,88</t>
+          <t>29,06; 39,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,94; 30,05</t>
+          <t>21,67; 29,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,86; 29,48</t>
+          <t>20,8; 28,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,66; 51,22</t>
+          <t>42,47; 51,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,67; 30,69</t>
+          <t>21,3; 30,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,79; 27,48</t>
+          <t>19,04; 28,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,97; 33,02</t>
+          <t>23,6; 32,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,14; 44,22</t>
+          <t>32,01; 43,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,59; 31,09</t>
+          <t>22,99; 31,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,13; 33,32</t>
+          <t>24,37; 33,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 38,94</t>
+          <t>29,22; 38,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,69; 39,35</t>
+          <t>31,68; 39,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 29,41</t>
+          <t>23,08; 29,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,9; 29,1</t>
+          <t>23,09; 29,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,07; 34,91</t>
+          <t>27,63; 34,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 40,1</t>
+          <t>32,98; 40,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 36,76</t>
+          <t>24,32; 36,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 29,57</t>
+          <t>19,56; 29,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,25; 27,57</t>
+          <t>18,35; 27,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 28,83</t>
+          <t>19,21; 28,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 30,93</t>
+          <t>21,2; 31,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,66</t>
+          <t>25,16; 35,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 30,06</t>
+          <t>20,55; 30,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,8; 31,32</t>
+          <t>22,79; 31,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 31,87</t>
+          <t>23,82; 32,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,61; 31,15</t>
+          <t>24,0; 30,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,65</t>
+          <t>20,35; 27,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 28,59</t>
+          <t>22,17; 28,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 35,67</t>
+          <t>24,21; 35,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,27; 34,8</t>
+          <t>24,15; 35,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 30,18</t>
+          <t>20,44; 30,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,83; 56,99</t>
+          <t>43,38; 57,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,88; 34,38</t>
+          <t>24,2; 33,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 36,04</t>
+          <t>25,14; 35,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 30,12</t>
+          <t>20,64; 30,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,04; 47,37</t>
+          <t>23,02; 47,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,67; 32,95</t>
+          <t>25,65; 33,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,08; 33,52</t>
+          <t>26,51; 34,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,66; 28,73</t>
+          <t>21,99; 28,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 48,84</t>
+          <t>30,71; 49,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,18; 26,8</t>
+          <t>14,85; 26,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 29,33</t>
+          <t>17,42; 29,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,44; 75,28</t>
+          <t>58,09; 75,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,73; 90,4</t>
+          <t>82,66; 90,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 31,32</t>
+          <t>18,43; 31,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,05; 34,68</t>
+          <t>21,81; 34,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,61; 76,15</t>
+          <t>61,53; 76,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,23; 90,75</t>
+          <t>84,56; 90,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,63; 26,92</t>
+          <t>18,24; 27,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,0; 30,34</t>
+          <t>21,45; 29,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,56; 73,53</t>
+          <t>62,89; 74,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 90,1</t>
+          <t>84,99; 90,12</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,72; 42,81</t>
+          <t>29,11; 42,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,16; 37,07</t>
+          <t>24,59; 37,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 29,56</t>
+          <t>17,9; 29,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,81; 22,91</t>
+          <t>13,57; 22,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,94; 40,21</t>
+          <t>26,17; 39,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,48; 32,43</t>
+          <t>21,42; 32,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,86; 37,89</t>
+          <t>25,71; 37,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,88; 24,72</t>
+          <t>16,43; 24,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,45; 39,18</t>
+          <t>29,45; 39,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,84; 32,94</t>
+          <t>24,87; 32,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,04; 32,01</t>
+          <t>23,45; 31,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,24</t>
+          <t>15,92; 22,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,73; 31,23</t>
+          <t>22,58; 31,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,95; 31,05</t>
+          <t>24,18; 31,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,89; 37,14</t>
+          <t>27,57; 36,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,16; 51,84</t>
+          <t>42,25; 51,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,67; 29,24</t>
+          <t>21,94; 29,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,21; 35,96</t>
+          <t>28,06; 35,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,74; 38,98</t>
+          <t>29,92; 38,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,28; 81,83</t>
+          <t>45,39; 82,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,23; 28,81</t>
+          <t>23,17; 28,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,36; 32,66</t>
+          <t>27,03; 32,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,08; 36,28</t>
+          <t>30,28; 36,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,63; 71,88</t>
+          <t>45,98; 71,58</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,92; 34,34</t>
+          <t>26,4; 34,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,71; 46,04</t>
+          <t>38,12; 45,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,23; 57,27</t>
+          <t>49,06; 56,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,5; 64,47</t>
+          <t>21,65; 64,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,64; 38,07</t>
+          <t>30,23; 37,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,96; 41,7</t>
+          <t>34,16; 41,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,02; 56,24</t>
+          <t>48,59; 56,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>65,87; 72,03</t>
+          <t>65,92; 71,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,23; 34,91</t>
+          <t>29,44; 35,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36,89; 42,37</t>
+          <t>37,11; 42,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,85; 55,44</t>
+          <t>49,65; 55,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,54; 66,96</t>
+          <t>35,52; 66,88</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,63</t>
+          <t>26,83; 30,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27,84; 31,4</t>
+          <t>27,93; 31,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,01; 36,66</t>
+          <t>32,92; 36,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,83; 47,58</t>
+          <t>34,02; 47,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,81</t>
+          <t>27,3; 30,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,73; 33,05</t>
+          <t>29,37; 32,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,21; 39,06</t>
+          <t>35,29; 38,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46,02; 59,53</t>
+          <t>45,82; 58,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,57; 30,16</t>
+          <t>27,63; 30,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,42; 31,81</t>
+          <t>29,25; 31,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34,7; 37,32</t>
+          <t>34,8; 37,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,91; 50,97</t>
+          <t>42,19; 50,88</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48189; 73935</t>
+          <t>50074; 75711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50257; 77753</t>
+          <t>49319; 77420</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44759; 71965</t>
+          <t>43901; 71677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124753; 168271</t>
+          <t>123484; 166878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56992; 85209</t>
+          <t>56994; 84794</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51984; 81171</t>
+          <t>51077; 79350</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50340; 77886</t>
+          <t>50774; 78877</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>116525; 146035</t>
+          <t>117461; 146205</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113150; 152679</t>
+          <t>114130; 153396</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110115; 150795</t>
+          <t>108727; 148851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102540; 144904</t>
+          <t>102227; 141266</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>253001; 303767</t>
+          <t>251861; 304290</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88793; 125774</t>
+          <t>87298; 123690</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76148; 111388</t>
+          <t>77179; 113850</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83420; 119912</t>
+          <t>85713; 119145</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162931; 224165</t>
+          <t>162301; 220625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>99444; 136870</t>
+          <t>101204; 139266</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105653; 145884</t>
+          <t>106711; 146035</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116162; 153145</t>
+          <t>114942; 150897</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>158922; 197382</t>
+          <t>158915; 197814</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>197465; 249975</t>
+          <t>196190; 250046</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193064; 245373</t>
+          <t>194637; 246858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212355; 264086</t>
+          <t>208992; 260105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>331690; 404453</t>
+          <t>332627; 405496</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>58954; 86957</t>
+          <t>57530; 87434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56551; 86542</t>
+          <t>57236; 87037</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53011; 80095</t>
+          <t>53295; 80300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57347; 86562</t>
+          <t>57661; 85947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59576; 89319</t>
+          <t>61226; 90460</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82860; 117232</t>
+          <t>82716; 117613</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62800; 92499</t>
+          <t>63261; 95193</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76432; 105020</t>
+          <t>76415; 106582</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125795; 167415</t>
+          <t>125126; 170290</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146704; 193589</t>
+          <t>149149; 191417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124890; 165409</t>
+          <t>121773; 164343</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>139815; 181703</t>
+          <t>140875; 182322</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65068; 95441</t>
+          <t>64763; 94150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75997; 108953</t>
+          <t>75593; 110124</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67335; 99618</t>
+          <t>67462; 99454</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132833; 176730</t>
+          <t>134519; 178966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71543; 102988</t>
+          <t>72490; 101290</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87971; 123548</t>
+          <t>86194; 121332</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71167; 105064</t>
+          <t>71994; 105046</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>109100; 224276</t>
+          <t>108972; 223590</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>145576; 186820</t>
+          <t>145478; 188059</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171038; 219839</t>
+          <t>173880; 223034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>147053; 195045</t>
+          <t>149282; 193354</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>238260; 382715</t>
+          <t>240616; 384655</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25847; 45641</t>
+          <t>25281; 45790</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32988; 56329</t>
+          <t>33459; 57257</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69670; 89747</t>
+          <t>69259; 89806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139340; 152253</t>
+          <t>139221; 152903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31598; 54473</t>
+          <t>32051; 55248</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42912; 67478</t>
+          <t>42430; 67468</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89641; 110795</t>
+          <t>89520; 111066</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>170397; 183584</t>
+          <t>171056; 183979</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>64110; 92657</t>
+          <t>62774; 93187</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81199; 117305</t>
+          <t>82922; 115763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165612; 194637</t>
+          <t>166474; 196722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>315286; 334024</t>
+          <t>315087; 334087</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54359; 81018</t>
+          <t>55091; 81224</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62890; 92666</t>
+          <t>61477; 94063</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42561; 69068</t>
+          <t>41812; 69076</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35043; 58124</t>
+          <t>34420; 57832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54808; 81822</t>
+          <t>53247; 81356</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56874; 85885</t>
+          <t>56727; 85236</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63910; 93633</t>
+          <t>63540; 93708</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39128; 60890</t>
+          <t>40466; 59720</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115644; 153865</t>
+          <t>115679; 154427</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127887; 169583</t>
+          <t>128030; 168369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115557; 153902</t>
+          <t>112757; 153317</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>81021; 111240</t>
+          <t>79594; 111751</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105550; 145023</t>
+          <t>104846; 144942</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>137502; 178227</t>
+          <t>138788; 181847</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123368; 164263</t>
+          <t>121940; 163329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253149; 311258</t>
+          <t>253688; 311207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116889; 157720</t>
+          <t>118335; 160071</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>176613; 225082</t>
+          <t>175658; 224370</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>144836; 189876</t>
+          <t>145710; 187825</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>375066; 677838</t>
+          <t>375999; 682808</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>233193; 289148</t>
+          <t>232559; 289365</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>328332; 391981</t>
+          <t>324334; 392241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>279552; 337216</t>
+          <t>281393; 339273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>651926; 1026997</t>
+          <t>656983; 1022653</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>136241; 180472</t>
+          <t>138724; 179196</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>239052; 291848</t>
+          <t>241641; 291250</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>315201; 366677</t>
+          <t>314079; 363338</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>177180; 585836</t>
+          <t>196693; 586079</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>181257; 225154</t>
+          <t>178809; 224546</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>238526; 292834</t>
+          <t>239914; 293906</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>331957; 388813</t>
+          <t>335949; 390471</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>463671; 507030</t>
+          <t>464060; 506712</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>326544; 389922</t>
+          <t>328834; 392035</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>492916; 566101</t>
+          <t>495867; 565978</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>663795; 738241</t>
+          <t>661181; 737249</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>508597; 1079836</t>
+          <t>572801; 1078453</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>660275; 751819</t>
+          <t>658676; 746373</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>810594; 914182</t>
+          <t>813097; 915239</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>879600; 976764</t>
+          <t>877134; 974335</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1134610; 1595896</t>
+          <t>1140942; 1588859</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>754103; 843476</t>
+          <t>747514; 844575</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>935900; 1040413</t>
+          <t>924557; 1035890</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1009448; 1119982</t>
+          <t>1011762; 1112294</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1646831; 2130632</t>
+          <t>1639898; 2089353</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1431757; 1566168</t>
+          <t>1434830; 1562899</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1782601; 1927511</t>
+          <t>1772288; 1921758</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1919510; 2064428</t>
+          <t>1924967; 2070108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2905594; 3533389</t>
+          <t>2925284; 3527322</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,15; 39,54</t>
+          <t>26,24; 39,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 30,9</t>
+          <t>19,63; 30,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 29,23</t>
+          <t>18,59; 29,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,43; 54,64</t>
+          <t>41,01; 52,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 42,14</t>
+          <t>28,41; 41,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,33; 31,59</t>
+          <t>20,72; 32,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,02</t>
+          <t>20,67; 31,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,84; 50,83</t>
+          <t>43,16; 52,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 39,06</t>
+          <t>29,14; 38,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,67; 29,66</t>
+          <t>21,65; 29,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 28,74</t>
+          <t>21,01; 29,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,47; 51,31</t>
+          <t>43,65; 51,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 30,19</t>
+          <t>21,57; 30,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,09</t>
+          <t>18,86; 28,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,6; 32,81</t>
+          <t>23,84; 33,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,01; 43,52</t>
+          <t>30,7; 41,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,99; 31,64</t>
+          <t>22,93; 31,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,37; 33,35</t>
+          <t>24,1; 33,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 38,36</t>
+          <t>29,18; 38,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,68; 39,44</t>
+          <t>31,64; 39,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 29,42</t>
+          <t>23,38; 29,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 29,28</t>
+          <t>22,85; 28,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,63; 34,38</t>
+          <t>27,51; 34,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,98; 40,21</t>
+          <t>32,82; 39,63</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,32; 36,96</t>
+          <t>24,77; 37,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,56; 29,74</t>
+          <t>19,12; 29,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 27,64</t>
+          <t>18,46; 27,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 28,63</t>
+          <t>18,68; 28,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,2; 31,32</t>
+          <t>20,71; 31,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,16; 35,78</t>
+          <t>25,39; 35,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,55; 30,93</t>
+          <t>20,86; 30,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,79; 31,79</t>
+          <t>22,57; 30,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,82; 32,41</t>
+          <t>24,24; 31,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,0; 30,8</t>
+          <t>23,93; 31,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,35; 27,47</t>
+          <t>21,0; 27,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 28,69</t>
+          <t>21,95; 28,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,21; 35,19</t>
+          <t>24,42; 35,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,15; 35,17</t>
+          <t>24,62; 35,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,44; 30,13</t>
+          <t>20,88; 30,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,38; 57,71</t>
+          <t>42,92; 56,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,2; 33,82</t>
+          <t>23,79; 34,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 35,39</t>
+          <t>25,57; 35,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 30,11</t>
+          <t>20,42; 29,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,02; 47,22</t>
+          <t>42,34; 52,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,65; 33,16</t>
+          <t>25,68; 33,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 34,0</t>
+          <t>26,24; 33,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,99; 28,48</t>
+          <t>21,53; 28,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 49,09</t>
+          <t>44,44; 52,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,85; 26,89</t>
+          <t>15,36; 26,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 29,81</t>
+          <t>17,09; 30,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,09; 75,33</t>
+          <t>59,2; 75,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,66; 90,78</t>
+          <t>81,16; 89,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,77</t>
+          <t>17,73; 31,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 34,67</t>
+          <t>23,08; 35,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,53; 76,33</t>
+          <t>61,56; 76,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,56; 90,95</t>
+          <t>83,92; 90,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,24; 27,07</t>
+          <t>18,19; 27,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 29,94</t>
+          <t>21,52; 30,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,89; 74,31</t>
+          <t>62,47; 73,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,99; 90,12</t>
+          <t>84,15; 89,24</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,11; 42,91</t>
+          <t>28,86; 42,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 37,63</t>
+          <t>25,33; 37,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,9; 29,57</t>
+          <t>18,34; 29,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,57; 22,79</t>
+          <t>13,49; 22,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,17; 39,98</t>
+          <t>27,29; 40,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,42; 32,19</t>
+          <t>21,82; 32,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,71; 37,92</t>
+          <t>26,01; 38,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,43; 24,24</t>
+          <t>16,18; 24,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,45; 39,32</t>
+          <t>29,37; 39,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,87; 32,71</t>
+          <t>24,9; 32,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 31,89</t>
+          <t>23,23; 31,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,92; 22,35</t>
+          <t>16,01; 22,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,58; 31,22</t>
+          <t>22,58; 30,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,18; 31,68</t>
+          <t>23,94; 31,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,57; 36,93</t>
+          <t>27,73; 36,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,25; 51,83</t>
+          <t>41,87; 50,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,94; 29,68</t>
+          <t>22,1; 29,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,06; 35,84</t>
+          <t>28,27; 35,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,92; 38,56</t>
+          <t>29,76; 38,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,39; 82,43</t>
+          <t>42,11; 49,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,17; 28,83</t>
+          <t>23,31; 28,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,03; 32,68</t>
+          <t>27,2; 32,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,51</t>
+          <t>30,08; 36,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,98; 71,58</t>
+          <t>43,09; 48,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,4; 34,1</t>
+          <t>26,08; 33,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,12; 45,95</t>
+          <t>37,55; 45,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,06; 56,75</t>
+          <t>49,16; 57,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,65; 64,5</t>
+          <t>59,51; 66,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 37,96</t>
+          <t>30,16; 37,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,16; 41,85</t>
+          <t>34,03; 41,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,59; 56,48</t>
+          <t>47,87; 56,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>65,92; 71,98</t>
+          <t>65,92; 71,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,44; 35,1</t>
+          <t>29,11; 34,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37,11; 42,36</t>
+          <t>37,06; 42,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,65; 55,37</t>
+          <t>49,62; 55,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,52; 66,88</t>
+          <t>64,09; 68,42</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,83; 30,41</t>
+          <t>26,88; 30,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27,93; 31,43</t>
+          <t>27,83; 31,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,92; 36,57</t>
+          <t>32,97; 36,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,02; 47,37</t>
+          <t>45,16; 49,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,85</t>
+          <t>27,48; 30,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,37; 32,9</t>
+          <t>29,4; 32,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,79</t>
+          <t>35,27; 39,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45,82; 58,38</t>
+          <t>47,25; 50,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,63; 30,1</t>
+          <t>27,61; 30,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29,25; 31,71</t>
+          <t>29,34; 31,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34,8; 37,42</t>
+          <t>34,79; 37,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,19; 50,88</t>
+          <t>46,59; 49,1</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146886</t>
+          <t>141477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>130754</t>
+          <t>147865</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>277640</t>
+          <t>289342</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50074; 75711</t>
+          <t>50256; 75219</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49319; 77420</t>
+          <t>49191; 77240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43901; 71677</t>
+          <t>45580; 72220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123484; 166878</t>
+          <t>123408; 158441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56994; 84794</t>
+          <t>57158; 84364</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51077; 79350</t>
+          <t>52057; 81711</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50774; 78877</t>
+          <t>50909; 78634</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>117461; 146205</t>
+          <t>133559; 163170</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114130; 153396</t>
+          <t>114429; 150660</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108727; 148851</t>
+          <t>108637; 148676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102227; 141266</t>
+          <t>103263; 142734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>251861; 304290</t>
+          <t>266445; 313787</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190856</t>
+          <t>190742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>178033</t>
+          <t>187994</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>368889</t>
+          <t>378737</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87298; 123690</t>
+          <t>88368; 123878</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77179; 113850</t>
+          <t>76429; 114433</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85713; 119145</t>
+          <t>86573; 122018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162301; 220625</t>
+          <t>159052; 216906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>101204; 139266</t>
+          <t>100953; 138599</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106711; 146035</t>
+          <t>105507; 144896</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>114942; 150897</t>
+          <t>114778; 152611</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>158915; 197814</t>
+          <t>168205; 207869</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>196190; 250046</t>
+          <t>198722; 249455</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194637; 246858</t>
+          <t>192641; 243482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>208992; 260105</t>
+          <t>208092; 260243</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>332627; 405496</t>
+          <t>344462; 415992</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>90507</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>161334</t>
+          <t>159933</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57530; 87434</t>
+          <t>58588; 88592</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57236; 87037</t>
+          <t>55954; 85709</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53295; 80300</t>
+          <t>53636; 79878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57661; 85947</t>
+          <t>55919; 84151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61226; 90460</t>
+          <t>59803; 89787</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82716; 117613</t>
+          <t>83484; 117088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63261; 95193</t>
+          <t>64187; 94048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76415; 106582</t>
+          <t>77124; 105059</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125126; 170290</t>
+          <t>127328; 168003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149149; 191417</t>
+          <t>148690; 195763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121773; 164343</t>
+          <t>125643; 165330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>140875; 182322</t>
+          <t>140697; 180666</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>185786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>176231</t>
+          <t>197614</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>332191</t>
+          <t>383400</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64763; 94150</t>
+          <t>65337; 94414</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75593; 110124</t>
+          <t>77075; 109598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67462; 99454</t>
+          <t>68911; 101105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>134519; 178966</t>
+          <t>159128; 209280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72490; 101290</t>
+          <t>71252; 102409</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86194; 121332</t>
+          <t>87657; 120923</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71994; 105046</t>
+          <t>71232; 104335</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>108972; 223590</t>
+          <t>177658; 218390</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>145478; 188059</t>
+          <t>145619; 189128</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>173880; 223034</t>
+          <t>172112; 220013</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149282; 193354</t>
+          <t>146140; 194610</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>240616; 384655</t>
+          <t>351226; 416345</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>162063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>178082</t>
+          <t>193369</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>324738</t>
+          <t>355433</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25281; 45790</t>
+          <t>26154; 45185</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33459; 57257</t>
+          <t>32817; 57806</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69259; 89806</t>
+          <t>70579; 90045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139221; 152903</t>
+          <t>153631; 169788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32051; 55248</t>
+          <t>30836; 54699</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42430; 67468</t>
+          <t>44908; 68955</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89520; 111066</t>
+          <t>89564; 111094</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>171056; 183979</t>
+          <t>184448; 199094</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62774; 93187</t>
+          <t>62622; 93531</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82922; 115763</t>
+          <t>83210; 118034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166474; 196722</t>
+          <t>165363; 195245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>315087; 334087</t>
+          <t>344256; 365078</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>44075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95488</t>
+          <t>94120</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55091; 81224</t>
+          <t>54630; 80324</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61477; 94063</t>
+          <t>63327; 92605</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41812; 69076</t>
+          <t>42841; 68162</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34420; 57832</t>
+          <t>33691; 57021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53247; 81356</t>
+          <t>55526; 81900</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56727; 85236</t>
+          <t>57774; 86516</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63540; 93708</t>
+          <t>64270; 94218</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40466; 59720</t>
+          <t>40708; 61336</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115679; 154427</t>
+          <t>115367; 153814</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128030; 168369</t>
+          <t>128163; 168871</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112757; 153317</t>
+          <t>111691; 151714</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79594; 111751</t>
+          <t>80242; 110290</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>283080</t>
+          <t>322414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>494480</t>
+          <t>337285</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>777561</t>
+          <t>659699</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>104846; 144942</t>
+          <t>104841; 142364</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>138788; 181847</t>
+          <t>137415; 182421</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121940; 163329</t>
+          <t>122634; 163527</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253688; 311207</t>
+          <t>292544; 352906</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>118335; 160071</t>
+          <t>119216; 158458</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>175658; 224370</t>
+          <t>176965; 224895</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>145710; 187825</t>
+          <t>144923; 187591</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>375999; 682808</t>
+          <t>312230; 364023</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>232559; 289365</t>
+          <t>233973; 289734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>324334; 392241</t>
+          <t>326360; 392953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>281393; 339273</t>
+          <t>279553; 341433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>656983; 1022653</t>
+          <t>620456; 700712</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>420558</t>
+          <t>486282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>484425</t>
+          <t>558885</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>904983</t>
+          <t>1045167</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>138724; 179196</t>
+          <t>137069; 177949</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>241641; 291250</t>
+          <t>238000; 289458</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>314079; 363338</t>
+          <t>314734; 365989</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>196693; 586079</t>
+          <t>458874; 514709</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>178809; 224546</t>
+          <t>178383; 223094</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>239914; 293906</t>
+          <t>239022; 292634</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>335949; 390471</t>
+          <t>330951; 387346</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>464060; 506712</t>
+          <t>534130; 580093</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>328834; 392035</t>
+          <t>325166; 388542</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>495867; 565978</t>
+          <t>495221; 571515</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>661181; 737249</t>
+          <t>660705; 732803</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>572801; 1078453</t>
+          <t>1013528; 1082018</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>658676; 746373</t>
+          <t>659841; 748681</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>813097; 915239</t>
+          <t>810338; 915626</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>877134; 974335</t>
+          <t>878313; 979996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1140942; 1588859</t>
+          <t>1534252; 1669016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>747514; 844575</t>
+          <t>752463; 845461</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>924557; 1035890</t>
+          <t>925666; 1036465</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1011762; 1112294</t>
+          <t>1011202; 1118218</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1639898; 2089353</t>
+          <t>1713086; 1816654</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1434830; 1562899</t>
+          <t>1433902; 1560556</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1772288; 1921758</t>
+          <t>1778019; 1922867</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1924967; 2070108</t>
+          <t>1924204; 2069709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2925284; 3527322</t>
+          <t>3272423; 3448444</t>
         </is>
       </c>
     </row>
